--- a/BA/Part 1_Stakeholder Analysis amp Management-20260912/Artifacts/1. Stakeholder Register_VNS.xlsx
+++ b/BA/Part 1_Stakeholder Analysis amp Management-20260912/Artifacts/1. Stakeholder Register_VNS.xlsx
@@ -873,7 +873,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Meet their needs</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -913,17 +913,17 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Official report</t>
+          <t>Monitoring of national regulation</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>Once per semester</t>
+          <t>Ad hoc, if regulation changes</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>Not involved in day-to-day work, but defines the regulatory requirements for educational IT systems and sector funding. Communication is formal reporting at control points only.</t>
+          <t>Formal sponsor of the sector, but for a pilot inside a single department the ministry has neither influence over delivery nor day-to-day interest in it. Monitored only in case the national regulation of educational IT systems changes; no recurring communication and no project activity is assigned to it.</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Project team “VNS”, group SHI-2025</t>
+          <t>Project team “20/80”, group SHI-2025</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>12 S. Bandery Street, Lviv, 79013, Ukraine</t>
+          <t>5 Lukasha Street, Lviv, Ukraine</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Project team “VNS”, group SHI-2025</t>
+          <t>Project team “20/80”, group SHI-2025</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>12 S. Bandery Street, Lviv, 79013, Ukraine</t>
+          <t>5 Lukasha Street, Lviv, Ukraine</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Project team “VNS”, group SHI-2025</t>
+          <t>Project team “20/80”, group SHI-2025</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>12 S. Bandery Street, Lviv, 79013, Ukraine</t>
+          <t>5 Lukasha Street, Lviv, Ukraine</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>Project team “VNS”, group SHI-2025</t>
+          <t>Project team “20/80”, group SHI-2025</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>12 S. Bandery Street, Lviv, 79013, Ukraine</t>
+          <t>5 Lukasha Street, Lviv, Ukraine</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Project team “VNS”, group SHI-2025</t>
+          <t>Project team “20/80”, group SHI-2025</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>12 S. Bandery Street, Lviv, 79013, Ukraine</t>
+          <t>5 Lukasha Street, Lviv, Ukraine</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Project team “VNS”, group SHI-2025</t>
+          <t>Project team “20/80”, group SHI-2025</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>12 S. Bandery Street, Lviv, 79013, Ukraine</t>
+          <t>5 Lukasha Street, Lviv, Ukraine</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>The approved stakeholder list contains nobody with both low influence and low interest, so the MONITOR quadrant is deliberately left empty.</t>
+          <t>The Ministry of Education and Science sits here: for a pilot inside a single department it has neither influence over delivery nor day-to-day interest, so it carries no RACI column and no recurring communication.</t>
         </is>
       </c>
     </row>

--- a/BA/Part 1_Stakeholder Analysis amp Management-20260912/Artifacts/1. Stakeholder Register_VNS.xlsx
+++ b/BA/Part 1_Stakeholder Analysis amp Management-20260912/Artifacts/1. Stakeholder Register_VNS.xlsx
@@ -527,19 +527,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="56" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="70" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="2" ht="26" customHeight="1">
@@ -793,7 +793,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="62" customHeight="1">
+    <row r="12" ht="74" customHeight="1">
       <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Lviv Polytechnic National University</t>
@@ -860,7 +860,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="62" customHeight="1">
+    <row r="13" ht="74" customHeight="1">
       <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Ministry of Education and Science of Ukraine</t>
@@ -927,7 +927,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="62" customHeight="1">
+    <row r="14" ht="74" customHeight="1">
       <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Nataliia Shakhovska</t>
@@ -994,7 +994,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="62" customHeight="1">
+    <row r="15" ht="74" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Nataliia Boiko</t>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="62" customHeight="1">
+    <row r="16" ht="74" customHeight="1">
       <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Technical Department of Lviv Polytechnic</t>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="62" customHeight="1">
+    <row r="17" ht="74" customHeight="1">
       <c r="B17" s="3" t="inlineStr">
         <is>
           <t>End users — Lviv Polytechnic students</t>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="62" customHeight="1">
+    <row r="18" ht="74" customHeight="1">
       <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Kostiantyn Holovskyi</t>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Project team “20/80”, group SHI-2025</t>
+          <t>Project team “20/80”</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1262,7 +1262,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="62" customHeight="1">
+    <row r="19" ht="74" customHeight="1">
       <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Nazar Zankovych</t>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Project team “20/80”, group SHI-2025</t>
+          <t>Project team “20/80”</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="62" customHeight="1">
+    <row r="20" ht="74" customHeight="1">
       <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Andrii Lysun</t>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Project team “20/80”, group SHI-2025</t>
+          <t>Project team “20/80”</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -1396,7 +1396,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="62" customHeight="1">
+    <row r="21" ht="74" customHeight="1">
       <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Denys Lunhul</t>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>Project team “20/80”, group SHI-2025</t>
+          <t>Project team “20/80”</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="62" customHeight="1">
+    <row r="22" ht="74" customHeight="1">
       <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Yaroslav Shevchuk</t>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Project team “20/80”, group SHI-2025</t>
+          <t>Project team “20/80”</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -1530,7 +1530,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="62" customHeight="1">
+    <row r="23" ht="74" customHeight="1">
       <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Volodymyr Kamelchuk</t>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Project team “20/80”, group SHI-2025</t>
+          <t>Project team “20/80”</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
